--- a/TASTI_SYNTHETIC/PnoChem.xlsx
+++ b/TASTI_SYNTHETIC/PnoChem.xlsx
@@ -431,19 +431,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>36W960M806</t>
+          <t>57M624X879</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Engine Flush</t>
+          <t>Coolant</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29Y732T634</t>
+          <t>96Q332D906</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,12 +455,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>83N966R507</t>
+          <t>16M768T328</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coolant</t>
+          <t>Lubricant</t>
         </is>
       </c>
     </row>
